--- a/artfynd/A 18158-2026 artfynd.xlsx
+++ b/artfynd/A 18158-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192926</v>
+        <v>130192927</v>
       </c>
       <c r="B2" t="n">
-        <v>104428</v>
+        <v>58676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688360</v>
+        <v>688395</v>
       </c>
       <c r="R2" t="n">
-        <v>6675704</v>
+        <v>6675721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192923</v>
+        <v>130192934</v>
       </c>
       <c r="B3" t="n">
-        <v>101146</v>
+        <v>99141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688305</v>
+        <v>688387</v>
       </c>
       <c r="R3" t="n">
-        <v>6675808</v>
+        <v>6675654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130192939</v>
+        <v>130192901</v>
       </c>
       <c r="B4" t="n">
-        <v>101146</v>
+        <v>106155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688407</v>
+        <v>688452</v>
       </c>
       <c r="R4" t="n">
-        <v>6675588</v>
+        <v>6675669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130192927</v>
+        <v>130192891</v>
       </c>
       <c r="B5" t="n">
-        <v>58574</v>
+        <v>102559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688395</v>
+        <v>688462</v>
       </c>
       <c r="R5" t="n">
-        <v>6675721</v>
+        <v>6675638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130192934</v>
+        <v>130192926</v>
       </c>
       <c r="B6" t="n">
-        <v>98979</v>
+        <v>104627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>688387</v>
+        <v>688360</v>
       </c>
       <c r="R6" t="n">
-        <v>6675654</v>
+        <v>6675704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192931</v>
+        <v>130192923</v>
       </c>
       <c r="B7" t="n">
-        <v>101146</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688370</v>
+        <v>688305</v>
       </c>
       <c r="R7" t="n">
-        <v>6675672</v>
+        <v>6675808</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192936</v>
+        <v>130192931</v>
       </c>
       <c r="B8" t="n">
-        <v>101146</v>
+        <v>101325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688388</v>
+        <v>688370</v>
       </c>
       <c r="R8" t="n">
-        <v>6675631</v>
+        <v>6675672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1456,6 +1456,230 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130192936</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>688388</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6675631</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>NVI (C250181) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130192939</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>688407</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6675588</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>NVI (C250181) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
